--- a/grupos/6ALCM - Estadisticos 20232.xlsx
+++ b/grupos/6ALCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -203,18 +203,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Gerson Hermenegildo</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
@@ -228,57 +228,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
-    <t>JOSE ANGEL</t>
-  </si>
-  <si>
-    <t>ISAI</t>
   </si>
 </sst>
 </file>
@@ -786,22 +735,22 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -822,22 +771,22 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -863,22 +812,22 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -908,13 +857,13 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -940,22 +889,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -985,10 +934,10 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1017,22 +966,22 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1056,7 +1005,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1065,10 +1014,10 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1094,22 +1043,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1133,19 +1082,19 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
+        <v>7</v>
+      </c>
+      <c r="W8">
         <v>6</v>
       </c>
-      <c r="W8">
-        <v>7</v>
-      </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1171,22 +1120,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1216,10 +1165,10 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1248,22 +1197,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1293,13 +1242,13 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1325,22 +1274,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1370,10 +1319,10 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1396,28 +1345,28 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12">
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1444,13 +1393,13 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1479,22 +1428,22 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1515,22 +1464,22 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1550,28 +1499,28 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G14">
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1598,16 +1547,16 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1633,22 +1582,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1710,22 +1659,22 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1752,16 +1701,16 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1781,28 +1730,28 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1835,10 +1784,10 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1858,28 +1807,28 @@
         <v>8</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1900,22 +1849,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1941,22 +1890,22 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2018,22 +1967,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2095,22 +2044,22 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2140,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2172,22 +2121,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2220,7 +2169,7 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2243,28 +2192,28 @@
         <v>8</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2291,16 +2240,16 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2326,22 +2275,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2368,16 +2317,16 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2397,28 +2346,28 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25">
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2451,10 +2400,10 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2480,22 +2429,22 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2522,13 +2471,13 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2557,22 +2506,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2599,13 +2548,13 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2634,22 +2583,22 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2676,16 +2625,16 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2711,22 +2660,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2747,22 +2696,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2788,22 +2737,22 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2839,7 +2788,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2865,22 +2814,22 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2942,22 +2891,22 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2990,10 +2939,10 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3019,22 +2968,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3096,22 +3045,22 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3147,7 +3096,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3173,22 +3122,22 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3218,13 +3167,13 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3250,22 +3199,22 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3286,22 +3235,22 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>10</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3327,22 +3276,22 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3363,16 +3312,16 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>10</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>7</v>
@@ -3404,22 +3353,22 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3440,22 +3389,22 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>10</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3481,22 +3430,22 @@
         <v>9</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3526,13 +3475,13 @@
         <v>10</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3558,22 +3507,22 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3600,13 +3549,13 @@
         <v>10</v>
       </c>
       <c r="V40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -3745,40 +3694,40 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I4">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O4">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3804,40 +3753,40 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>87.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I5">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N5">
-        <v>87.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O5">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3878,7 +3827,7 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -3896,7 +3845,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3922,16 +3871,16 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>92.5</v>
+        <v>92</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3940,16 +3889,16 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>92.5</v>
+        <v>92</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3981,40 +3930,40 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I8">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N8">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O8">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4040,17 +3989,17 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>92.5</v>
+        <v>92</v>
       </c>
       <c r="I9">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
         <v>90</v>
       </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
-      <c r="K9">
-        <v>86.7</v>
-      </c>
       <c r="L9">
         <v>100</v>
       </c>
@@ -4058,16 +4007,16 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>92.5</v>
+        <v>92</v>
       </c>
       <c r="O9">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
         <v>90</v>
-      </c>
-      <c r="P9">
-        <v>100</v>
-      </c>
-      <c r="Q9">
-        <v>86.7</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4099,16 +4048,16 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J10">
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4117,16 +4066,16 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4158,10 +4107,10 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -4176,10 +4125,10 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -4217,10 +4166,10 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4235,10 +4184,10 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4276,40 +4225,40 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>92.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N13">
-        <v>92.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4335,40 +4284,40 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I14">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N14">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O14">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4394,10 +4343,10 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4412,10 +4361,10 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4462,7 +4411,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4480,7 +4429,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4512,7 +4461,7 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -4530,7 +4479,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4571,16 +4520,16 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>92.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I18">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4589,16 +4538,16 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>92.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O18">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4630,10 +4579,10 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4648,10 +4597,10 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4748,40 +4697,40 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4866,40 +4815,40 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="I23">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
         <v>90</v>
       </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
-      <c r="K23">
-        <v>93.3</v>
-      </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N23">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="O23">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
         <v>90</v>
       </c>
-      <c r="P23">
-        <v>100</v>
-      </c>
-      <c r="Q23">
-        <v>93.3</v>
-      </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4934,7 +4883,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4952,7 +4901,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4984,10 +4933,10 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -5002,10 +4951,10 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -5043,40 +4992,40 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>95</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I26">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N26">
-        <v>95</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O26">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="P26">
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5111,7 +5060,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5129,7 +5078,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5161,10 +5110,10 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="I28">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -5179,10 +5128,10 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="O28">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5220,40 +5169,40 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P29">
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5279,40 +5228,40 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R30">
         <v>100</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5347,7 +5296,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5365,7 +5314,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5397,16 +5346,16 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -5415,16 +5364,16 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5465,7 +5414,7 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5483,7 +5432,7 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5515,10 +5464,10 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>92.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I34">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5533,10 +5482,10 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>92.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O34">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5583,7 +5532,7 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5601,7 +5550,7 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -5633,10 +5582,10 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I36">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="J36">
         <v>100</v>
@@ -5648,13 +5597,13 @@
         <v>100</v>
       </c>
       <c r="M36">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N36">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O36">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -5666,7 +5615,7 @@
         <v>100</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5692,40 +5641,40 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I37">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="L37">
         <v>100</v>
       </c>
       <c r="M37">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N37">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O37">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P37">
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="R37">
         <v>100</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5751,16 +5700,16 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>92.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I38">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -5769,16 +5718,16 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>92.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O38">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="P38">
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="R38">
         <v>100</v>
@@ -5819,13 +5768,13 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L39">
         <v>100</v>
       </c>
       <c r="M39">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N39">
         <v>100</v>
@@ -5837,13 +5786,13 @@
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="R39">
         <v>100</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -5878,7 +5827,7 @@
         <v>100</v>
       </c>
       <c r="K40">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L40">
         <v>100</v>
@@ -5896,7 +5845,7 @@
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="R40">
         <v>100</v>
@@ -5959,7 +5908,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -5968,19 +5917,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>86.5</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5991,28 +5940,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>37</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6023,10 +5972,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>37</v>
@@ -6055,7 +6004,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -6076,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6087,7 +6036,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -6108,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6140,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6190,7 +6139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6220,164 +6169,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920287</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920287</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920267</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920088</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920268</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920276</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920279</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6ALCM - Estadisticos 20232.xlsx
+++ b/grupos/6ALCM - Estadisticos 20232.xlsx
@@ -59,7 +59,7 @@
     <t>ACEVEDO VALENCIA YARELI</t>
   </si>
   <si>
-    <t>ARGÜELLO NARANJO ATZIN HEFZIBA</t>
+    <t>ARGUELLO NARANJO ATZIN HEFZIBA</t>
   </si>
   <si>
     <t>DE JESUS SORIANO NADIA</t>
@@ -753,22 +753,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -830,22 +830,22 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -907,22 +907,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -984,22 +984,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1061,34 +1061,34 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>7</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1138,22 +1138,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1165,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1215,22 +1215,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1292,22 +1292,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1369,22 +1369,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1446,22 +1446,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1470,7 +1470,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1523,22 +1523,22 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1600,22 +1600,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1677,22 +1677,22 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1710,7 +1710,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1754,22 +1754,22 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1831,22 +1831,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1864,7 +1864,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1908,22 +1908,22 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -1985,22 +1985,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2062,22 +2062,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2086,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2139,22 +2139,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2216,22 +2216,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2293,22 +2293,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2370,22 +2370,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2447,22 +2447,22 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2524,22 +2524,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2601,22 +2601,22 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2631,10 +2631,10 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2678,22 +2678,22 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2702,7 +2702,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -2755,22 +2755,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2832,22 +2832,22 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2909,22 +2909,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -2933,13 +2933,13 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -2986,22 +2986,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3063,22 +3063,22 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3087,7 +3087,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3140,22 +3140,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3217,22 +3217,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3244,13 +3244,13 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3294,22 +3294,22 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>8</v>
@@ -3318,7 +3318,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>7</v>
@@ -3371,28 +3371,28 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V38">
         <v>10</v>
@@ -3404,7 +3404,7 @@
         <v>9</v>
       </c>
       <c r="Y38">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3448,22 +3448,22 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3481,7 +3481,7 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3525,22 +3525,22 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -3712,22 +3712,22 @@
         <v>94.5</v>
       </c>
       <c r="N4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O4">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>88.3</v>
+        <v>91.8</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3771,22 +3771,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N5">
-        <v>88.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="O5">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3830,7 +3830,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3845,7 +3845,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3889,16 +3889,16 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O7">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>95</v>
+        <v>96.5</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3948,22 +3948,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N8">
-        <v>90.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O8">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>88.3</v>
+        <v>91.8</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4007,16 +4007,16 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>92</v>
+        <v>92.2</v>
       </c>
       <c r="O9">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4066,16 +4066,16 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="O10">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P10">
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4125,16 +4125,16 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O11">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4184,10 +4184,10 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O12">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4243,22 +4243,22 @@
         <v>98.2</v>
       </c>
       <c r="N13">
-        <v>90.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O13">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4302,22 +4302,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N14">
-        <v>92</v>
+        <v>92.2</v>
       </c>
       <c r="O14">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4361,10 +4361,10 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O15">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4429,7 +4429,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4479,7 +4479,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4538,16 +4538,16 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>96.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="O18">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4597,10 +4597,10 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>98.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O19">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4715,22 +4715,22 @@
         <v>98.2</v>
       </c>
       <c r="N21">
-        <v>98.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O21">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4774,7 +4774,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -4833,22 +4833,22 @@
         <v>98.2</v>
       </c>
       <c r="N23">
-        <v>94.3</v>
+        <v>93</v>
       </c>
       <c r="O23">
-        <v>86.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4892,7 +4892,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4901,7 +4901,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4951,10 +4951,10 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O25">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -5010,22 +5010,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N26">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O26">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="P26">
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5069,7 +5069,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -5078,7 +5078,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5128,10 +5128,10 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>94.3</v>
+        <v>93.8</v>
       </c>
       <c r="O28">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5187,22 +5187,22 @@
         <v>98.2</v>
       </c>
       <c r="N29">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O29">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P29">
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5246,22 +5246,22 @@
         <v>98.2</v>
       </c>
       <c r="N30">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="O30">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R30">
         <v>100</v>
       </c>
       <c r="S30">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5305,7 +5305,7 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5314,7 +5314,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>95</v>
+        <v>96.5</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5364,16 +5364,16 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O32">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5423,7 +5423,7 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -5432,7 +5432,7 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5482,10 +5482,10 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O34">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5550,7 +5550,7 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -5600,22 +5600,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N36">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="O36">
-        <v>81.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P36">
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R36">
         <v>100</v>
       </c>
       <c r="S36">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5659,22 +5659,22 @@
         <v>94.5</v>
       </c>
       <c r="N37">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O37">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P37">
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="R37">
         <v>100</v>
       </c>
       <c r="S37">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5718,16 +5718,16 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O38">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P38">
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>95</v>
+        <v>96.5</v>
       </c>
       <c r="R38">
         <v>100</v>
@@ -5777,22 +5777,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P39">
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R39">
         <v>100</v>
       </c>
       <c r="S39">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -5836,16 +5836,16 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O40">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P40">
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R40">
         <v>100</v>
@@ -5961,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5993,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6089,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
